--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486268_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486268_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8524</v>
+        <v>5.5664</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9248</v>
+        <v>2.3169</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9276</v>
+        <v>3.2495</v>
       </c>
       <c r="G2" t="n">
         <v>3.3041</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>3.439</v>
+        <v>1.153</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1703</v>
+        <v>0.5624</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2687</v>
+        <v>0.5906</v>
       </c>
       <c r="V2" t="n">
         <v>1.1093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1327</v>
+        <v>5.4298</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6176</v>
+        <v>2.668</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5152</v>
+        <v>2.7618</v>
       </c>
       <c r="G3" t="n">
         <v>2.6533</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.864</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5432</v>
+        <v>0.5936</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0238</v>
+        <v>0.2704</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2407</v>
+        <v>2.8756</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7656</v>
+        <v>0.9146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.475</v>
+        <v>1.961</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3313</v>
+        <v>1.3751</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1612</v>
+        <v>-0.7087</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4926</v>
+        <v>2.0838</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8375</v>
+        <v>1.0358</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1346</v>
+        <v>0.0397</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7029</v>
+        <v>0.9961</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5062</v>
+        <v>0.3393</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2959</v>
+        <v>-0.7484</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7897</v>
+        <v>1.0877</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="R4" t="n">
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.113</v>
+        <v>0.0655</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0156</v>
+        <v>-0.2511</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1286</v>
+        <v>0.3166</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1318</v>
+        <v>2.3939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3558</v>
+        <v>1.6106</v>
       </c>
       <c r="F5" t="n">
-        <v>1.776</v>
+        <v>0.7833</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3751</v>
+        <v>2.3313</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7087</v>
+        <v>-0.1612</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0838</v>
+        <v>2.4926</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0358</v>
+        <v>2.8375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0397</v>
+        <v>1.1346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9961</v>
+        <v>1.7029</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3393</v>
+        <v>-0.5062</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7484</v>
+        <v>-1.2959</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0877</v>
+        <v>0.7897</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6782</v>
+        <v>0.0403</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8099</v>
+        <v>-0.1394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1317</v>
+        <v>0.1796</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9043</v>
+        <v>1.5795</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4952</v>
+        <v>-0.9417</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4091</v>
+        <v>2.5212</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2572</v>
+        <v>0.0197</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.2372</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.302</v>
+        <v>-0.2175</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1455</v>
+        <v>-0.8336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2587</v>
+        <v>0.0246</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1131</v>
+        <v>-0.8582</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4027</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2138</v>
+        <v>0.2127</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1889</v>
+        <v>0.6407</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4214</v>
+        <v>0.2548</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3497</v>
+        <v>0.1094</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0717</v>
+        <v>0.1454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4755</v>
+        <v>0.9993</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4173</v>
+        <v>0.6827</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9418</v>
+        <v>0.3166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9598</v>
+        <v>-1.2572</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7725</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1873</v>
+        <v>-0.302</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8777</v>
+        <v>0.1455</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8395</v>
+        <v>0.2587</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>-0.1131</v>
       </c>
       <c r="M7" t="n">
-        <v>0.082</v>
+        <v>-1.4027</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.067</v>
+        <v>-1.2138</v>
       </c>
       <c r="O7" t="n">
-        <v>0.149</v>
+        <v>-0.1889</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8409</v>
+        <v>0.5164</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5396</v>
+        <v>0.5372</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3014</v>
+        <v>-0.0207</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>0.2588</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.998</v>
+        <v>1.2623</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0281</v>
+        <v>-1.0034</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0197</v>
+        <v>0.9598</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2372</v>
+        <v>0.7725</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2175</v>
+        <v>0.1873</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8336</v>
+        <v>0.8777</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0246</v>
+        <v>0.8395</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8582</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2127</v>
+        <v>-0.067</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6407</v>
+        <v>0.149</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2947</v>
+        <v>0.6243</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9469</v>
+        <v>0.3845</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3478</v>
+        <v>0.2397</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.812</v>
+        <v>-0.8462</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8326</v>
+        <v>-0.4305</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0205</v>
+        <v>-0.4156</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7451</v>
+        <v>-3.0823</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-2.2567</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7451</v>
+        <v>-0.8255</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7451</v>
+        <v>-1.3481</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.4134</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7451</v>
+        <v>-0.9347</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.7342</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.8433</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0205</v>
+        <v>-0.2196</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.0156</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0205</v>
+        <v>-0.204</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1507</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8169</v>
+        <v>-1.1715</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1164</v>
+        <v>-0.6583</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2994</v>
+        <v>-0.5132</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3341</v>
+        <v>-2.0103</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4415</v>
+        <v>-0.9912</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8925</v>
+        <v>-1.0192</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4279</v>
+        <v>-0.4252</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9577</v>
+        <v>0.8521</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4702</v>
+        <v>-1.2773</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9062</v>
+        <v>-1.5852</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4838</v>
+        <v>-1.8433</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4224</v>
+        <v>0.2582</v>
       </c>
       <c r="P10" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3219</v>
+        <v>-0.271</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1214</v>
+        <v>-0.0156</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4433</v>
+        <v>-0.2554</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7602</v>
+        <v>-0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8785</v>
+        <v>-1.6585</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3498</v>
+        <v>-2.6189</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5286999999999999</v>
+        <v>0.9604</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0823</v>
+        <v>-3.3341</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2567</v>
+        <v>-1.4415</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8255</v>
+        <v>-1.8925</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3481</v>
+        <v>-2.4279</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4134</v>
+        <v>-0.9577</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9347</v>
+        <v>-1.4702</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7342</v>
+        <v>-0.9062</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8433</v>
+        <v>-0.4838</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1091</v>
+        <v>-0.4224</v>
       </c>
       <c r="P11" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2519</v>
+        <v>0.4804</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9349</v>
+        <v>0.3761</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.317</v>
+        <v>0.1042</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1507</v>
+        <v>0.7602</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1507</v>
+        <v>0.9554</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1525</v>
+        <v>-1.7812</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5776</v>
+        <v>-1.8326</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5749</v>
+        <v>0.0514</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0103</v>
+        <v>-0.7451</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9912</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0192</v>
+        <v>-0.7451</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4252</v>
+        <v>-0.7451</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8521</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2773</v>
+        <v>-0.7451</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5852</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8433</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2582</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2519</v>
+        <v>0.0514</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9349</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.317</v>
+        <v>0.0514</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5731</v>
+        <v>-3.0052</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4402</v>
+        <v>-4.6565</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8671</v>
+        <v>1.6514</v>
       </c>
       <c r="G13" t="n">
         <v>-1.015</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3342</v>
+        <v>0.9022</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1512</v>
+        <v>0.9349</v>
       </c>
       <c r="U13" t="n">
-        <v>0.183</v>
+        <v>-0.0328</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9347</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.534399999999996</v>
+        <v>10.6407</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7383</v>
+        <v>-1.683400000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>12.2726</v>
+        <v>12.3244</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8006999999999993</v>
+        <v>-0.8006999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>-4.3028</v>
       </c>
       <c r="I14" t="n">
-        <v>3.502400000000001</v>
+        <v>3.5024</v>
       </c>
       <c r="J14" t="n">
         <v>2.8586</v>
@@ -1525,7 +1525,7 @@
         <v>3.8506</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9919000000000007</v>
+        <v>-0.9919000000000003</v>
       </c>
       <c r="M14" t="n">
         <v>-3.6595</v>
@@ -1537,7 +1537,7 @@
         <v>4.4941</v>
       </c>
       <c r="P14" t="n">
-        <v>4.35</v>
+        <v>4.349999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.8751</v>
@@ -1546,13 +1546,13 @@
         <v>15.2253</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3552</v>
+        <v>4.4617</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0216</v>
+        <v>3.0764</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3337</v>
+        <v>1.385</v>
       </c>
       <c r="V14" t="n">
         <v>2.629900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3566</v>
+        <v>2.9366</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5313</v>
+        <v>0.4196</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8252</v>
+        <v>2.517</v>
       </c>
       <c r="G15" t="n">
         <v>1.3545</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.697</v>
+        <v>0.277</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1214</v>
+        <v>-0.2331</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8183</v>
+        <v>0.5101</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7181</v>
+        <v>1.5313</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3962</v>
+        <v>0.7315</v>
       </c>
       <c r="F16" t="n">
-        <v>0.322</v>
+        <v>0.7998</v>
       </c>
       <c r="G16" t="n">
         <v>5.359</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3135</v>
+        <v>0.4996</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0397</v>
+        <v>0.3749</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3532</v>
+        <v>0.1247</v>
       </c>
       <c r="V16" t="n">
         <v>-1.4997</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1863</v>
+        <v>0.0196</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5134</v>
+        <v>-1.0608</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3271</v>
+        <v>1.0804</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2306</v>
+        <v>-0.5891</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7066</v>
+        <v>0.2341</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9372</v>
+        <v>-0.8232</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9935</v>
+        <v>0.1554</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4454</v>
+        <v>1.6639</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4519</v>
+        <v>-1.5084</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2241</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2612</v>
+        <v>-1.4298</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4854</v>
+        <v>0.6853</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5</v>
+        <v>-0.6736</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2019</v>
+        <v>-0.3016</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7019</v>
+        <v>-0.3719</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0207</v>
+        <v>1.4997</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0207</v>
+        <v>1.1093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6496</v>
+        <v>-0.3976</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.396</v>
+        <v>-0.8709</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7464</v>
+        <v>0.4733</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5891</v>
+        <v>-0.4544</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2341</v>
+        <v>-2.0409</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8232</v>
+        <v>1.5865</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1554</v>
+        <v>0.3086</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6639</v>
+        <v>-0.5927</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5084</v>
+        <v>0.9013</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7629</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4298</v>
+        <v>-1.4482</v>
       </c>
       <c r="O18" t="n">
         <v>0.6853</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3428</v>
+        <v>0.1884</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6369</v>
+        <v>0.4747</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7059</v>
+        <v>-0.2863</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4997</v>
+        <v>-0.3491</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3904</v>
+        <v>-0.3491</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.715</v>
+        <v>-0.5382</v>
       </c>
       <c r="E19" t="n">
-        <v>0.896</v>
+        <v>-0.7369</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.611</v>
+        <v>0.1987</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5862000000000001</v>
+        <v>-0.2306</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2858</v>
+        <v>2.7066</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3004</v>
+        <v>-2.9372</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9609</v>
+        <v>0.9935</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7696</v>
+        <v>2.4454</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1912</v>
+        <v>-1.4519</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3747</v>
+        <v>-1.2241</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4838</v>
+        <v>0.2612</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1091</v>
+        <v>-1.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6525</v>
+        <v>-0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4813</v>
+        <v>0.1481</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0227</v>
+        <v>-0.4254</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5414</v>
+        <v>0.5735</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.0207</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7983</v>
+        <v>-0.7663</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4238</v>
+        <v>-1.5955</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3744</v>
+        <v>0.8292</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4544</v>
+        <v>-0.876</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0409</v>
+        <v>0.8818</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5865</v>
+        <v>-1.7579</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3086</v>
+        <v>-0.2033</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5927</v>
+        <v>0.7696</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9013</v>
+        <v>-0.9729</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7629</v>
+        <v>-0.6727</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4482</v>
+        <v>0.1122</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6853</v>
+        <v>-0.7849</v>
       </c>
       <c r="P20" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2123</v>
+        <v>-0.1078</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9217</v>
+        <v>-0.4999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1341</v>
+        <v>0.392</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7272</v>
+        <v>-0.9334</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0425</v>
+        <v>0.2255</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3154</v>
+        <v>-1.1589</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.876</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8818</v>
+        <v>0.2858</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7579</v>
+        <v>0.3004</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2033</v>
+        <v>0.9609</v>
       </c>
       <c r="K21" t="n">
         <v>0.7696</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9729</v>
+        <v>0.1912</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6727</v>
+        <v>-0.3747</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1122</v>
+        <v>-0.4838</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7849</v>
+        <v>0.1091</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0687</v>
+        <v>0.2629</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9469</v>
+        <v>0.3521</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1217</v>
+        <v>-0.0892</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.955</v>
+        <v>-3.635</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.8649</v>
+        <v>-2.1851</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9099</v>
+        <v>-1.4499</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6723</v>
+        <v>-0.6767</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5845</v>
+        <v>1.8581</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0878</v>
+        <v>-2.5348</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.1917</v>
+        <v>0.2543</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9948</v>
+        <v>2.7739</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1969</v>
+        <v>-2.5196</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5194</v>
+        <v>-0.931</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4102</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1091</v>
+        <v>-0.0152</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1746</v>
+        <v>-0.3281</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4759</v>
+        <v>-0.2644</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6505</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5778</v>
+        <v>-4.5162</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8557</v>
+        <v>-7.2001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7222</v>
+        <v>2.6839</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6767</v>
+        <v>-3.6723</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8581</v>
+        <v>-1.5845</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5348</v>
+        <v>-2.0878</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2543</v>
+        <v>-4.1917</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7739</v>
+        <v>-1.9948</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5196</v>
+        <v>-2.1969</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.931</v>
+        <v>0.5194</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.4102</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0152</v>
+        <v>0.1091</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2709</v>
+        <v>-0.3866</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9349</v>
+        <v>-0.8111</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.336</v>
+        <v>0.4245</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.5345</v>
+        <v>-6.2992</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.2728</v>
+        <v>-12.2727</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7384</v>
+        <v>5.9735</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8005999999999996</v>
+        <v>0.8006000000000002</v>
       </c>
       <c r="H24" t="n">
         <v>4.302899999999999</v>
@@ -2314,7 +2314,7 @@
         <v>-3.8505</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9918000000000001</v>
+        <v>0.9917999999999998</v>
       </c>
       <c r="P24" t="n">
         <v>-4.350099999999999</v>
@@ -2326,16 +2326,16 @@
         <v>10.8752</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.3553</v>
+        <v>-0.1201</v>
       </c>
       <c r="T24" t="n">
         <v>-1.3338</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0216</v>
+        <v>1.2137</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.629799999999999</v>
+        <v>-2.6298</v>
       </c>
       <c r="W24" t="n">
         <v>0.6269</v>
